--- a/DAX函数.xlsx
+++ b/DAX函数.xlsx
@@ -1,25 +1,733 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="逻辑函数" sheetId="1" r:id="rId1"/>
+    <sheet name="文本函数" sheetId="2" r:id="rId2"/>
+    <sheet name="日期时间函数" sheetId="3" r:id="rId3"/>
+    <sheet name="判断函数" sheetId="4" r:id="rId4"/>
+    <sheet name="统计函数" sheetId="5" r:id="rId5"/>
+    <sheet name="时间智能函数" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="122211" fullCalcOnLoad="1"/>
+  <calcPr calcId="122211"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="226">
+  <si>
+    <t>AND(&lt;logical1&gt;,&lt;logical2&gt;)</t>
+  </si>
+  <si>
+    <t>检查是否两个参数均为 TRUE，并且在两个参数均为 TRUE 时返回 TRUE。 否则返回 False。</t>
+  </si>
+  <si>
+    <t>FALSE()</t>
+  </si>
+  <si>
+    <t>返回逻辑值 FALSE。</t>
+  </si>
+  <si>
+    <t>IF(logical_test&gt;,&lt;value_if_true&gt;, value_if_false)</t>
+  </si>
+  <si>
+    <t>检查是否满足作为第一个参数提供的条件。 如果该条件为 TRUE，则返回一个值；如果该条件为 FALSE，则返回另一个值。</t>
+  </si>
+  <si>
+    <t>IFERROR(value, value_if_error)</t>
+  </si>
+  <si>
+    <t>对某一表达式进行计算，并且如果该表达式返回错误则返回指定值，否则返回该表达式本身的值。</t>
+  </si>
+  <si>
+    <t>NOT(&lt;logical&gt;)</t>
+  </si>
+  <si>
+    <t>将 FALSE 更改为 TRUE，或者将 TRUE 更改为 FALSE。</t>
+  </si>
+  <si>
+    <t>OR(&lt;logical1&gt;,&lt;logical2&gt;)</t>
+  </si>
+  <si>
+    <t>检查参数之一是否为 TRUE 以返回 TRUE。 如果两个参数都是 FALSE，则该函数将返回 FALSE。</t>
+  </si>
+  <si>
+    <t>SWITCH(&lt;expression&gt;, &lt;value&gt;, &lt;result&gt;[, &lt;value&gt;, &lt;result&gt;]…[, &lt;else&gt;])</t>
+  </si>
+  <si>
+    <t>根据值列表计算表达式，并返回多个可能的结果表达式之一。</t>
+  </si>
+  <si>
+    <t>TRUE()</t>
+  </si>
+  <si>
+    <t>返回逻辑值 TRUE。</t>
+  </si>
+  <si>
+    <t>BLANK()</t>
+  </si>
+  <si>
+    <t>返回空白。</t>
+  </si>
+  <si>
+    <t>CONCATENATE(&lt;text1&gt;, &lt;text2&gt;)</t>
+  </si>
+  <si>
+    <t>将两个文本字符串联接成一个文本字符串。</t>
+  </si>
+  <si>
+    <t>EXACT(&lt;text1&gt;,&lt;text2&gt;)</t>
+  </si>
+  <si>
+    <t>比较两个文本字符串；如果它们完全相同则返回 TRUE，否则返回 FALSE。 EXACT 区分大小写但忽略格式上的差异。 可以使用 EXACT 测试输入到文档中的文本。</t>
+  </si>
+  <si>
+    <t>FIND(&lt;find_text&gt;, &lt;within_text&gt;[, [&lt;start_num&gt;][, &lt;NotFoundValue&gt;]])</t>
+  </si>
+  <si>
+    <t>FIXED(&lt;number&gt;, &lt;decimals&gt;, &lt;no_commas&gt;)</t>
+  </si>
+  <si>
+    <t>将数字舍入到指定的小数位数，并以文本形式返回结果。 可以指定以带或不带逗号的形式返回结果。</t>
+  </si>
+  <si>
+    <t>FORMAT(&lt;value&gt;, &lt;format_string&gt;)</t>
+  </si>
+  <si>
+    <t>根据指定的格式将值转换为文本。</t>
+  </si>
+  <si>
+    <t>返回一个文本字符串在另一文本字符串中的开始位置。 FIND 区分大小写。</t>
+  </si>
+  <si>
+    <t>LEFT(&lt;text&gt;, &lt;num_chars&gt;)</t>
+  </si>
+  <si>
+    <t>从文本字符串的开头返回指定数目的字符。</t>
+  </si>
+  <si>
+    <t>LEN(&lt;text&gt;)</t>
+  </si>
+  <si>
+    <t>返回文本字符串中的字符数。</t>
+  </si>
+  <si>
+    <t>LOWER(&lt;text&gt;)</t>
+  </si>
+  <si>
+    <t>将文本字符串中的所有字母都转换为小写。</t>
+  </si>
+  <si>
+    <t>MID(&lt;text&gt;, &lt;start_num&gt;, &lt;num_chars&gt;)</t>
+  </si>
+  <si>
+    <t>根据给出的开始位置和长度，从文本字符串的中间返回字符串。</t>
+  </si>
+  <si>
+    <t>REPLACE(&lt;old_text&gt;, &lt;start_num&gt;, &lt;num_chars&gt;, &lt;new_text&gt;)</t>
+  </si>
+  <si>
+    <t>REPLACE 将基于您指定的字符数，用不同的文本字符串替换文本字符串的一部分。</t>
+  </si>
+  <si>
+    <t>REPT(&lt;text&gt;, &lt;num_times&gt;)</t>
+  </si>
+  <si>
+    <t>重复给定次数的文本。 使用 REPT 可用一个文本字符串的许多实例填充单元格。</t>
+  </si>
+  <si>
+    <t>RIGHT(&lt;text&gt;, &lt;num_chars&gt;)</t>
+  </si>
+  <si>
+    <t>RIGHT 基于您指定的字符数，返回文本字符串中最后一个或几个字符。</t>
+  </si>
+  <si>
+    <t>SEARCH(&lt;find_text&gt;, &lt;within_text&gt;[, [&lt;start_num&gt;][, &lt;NotFoundValue&gt;]])</t>
+  </si>
+  <si>
+    <t>返回最先找到特定字符或文本字符串的位置的字符编号（从左向右算起）。 搜索不区分大小写，但区分重音。</t>
+  </si>
+  <si>
+    <t>SUBSTITUTE(&lt;text&gt;, &lt;old_text&gt;, &lt;new_text&gt;, &lt;instance_num&gt;)</t>
+  </si>
+  <si>
+    <t>用文本字符串中的新文本替换现有文本。</t>
+  </si>
+  <si>
+    <t>TRIM(&lt;text&gt;)</t>
+  </si>
+  <si>
+    <t>从文本中删除两个词之间除了单个空格外的所有空格。</t>
+  </si>
+  <si>
+    <t>UPPER (&lt;text&gt;)</t>
+  </si>
+  <si>
+    <t>将文本字符串全都转换为大写字母</t>
+  </si>
+  <si>
+    <t>VALUE(&lt;text&gt;)</t>
+  </si>
+  <si>
+    <t>将表示数字的文本字符串转换为数字。</t>
+  </si>
+  <si>
+    <t>DATE(&lt;year&gt;, &lt;month&gt;, &lt;day&gt;)</t>
+  </si>
+  <si>
+    <t>以 datetime 格式返回指定的日期。</t>
+  </si>
+  <si>
+    <t>DATEVALUE(date_text)</t>
+  </si>
+  <si>
+    <t>将文本形式的日期转换为日期时间格式的日期。</t>
+  </si>
+  <si>
+    <t>DAY(&lt;date&gt;)</t>
+  </si>
+  <si>
+    <t>返回月中的第几天，即一个 1 到 31 之间的数字。</t>
+  </si>
+  <si>
+    <t>EDATE(&lt;start_date&gt;, &lt;months&gt;)</t>
+  </si>
+  <si>
+    <t>返回在开始日期之前或之后指示的月数的日期。 使用 EDATE 可以计算与发行日属于月中同一天的到期日期。</t>
+  </si>
+  <si>
+    <t>EOMONTH(&lt;start_date&gt;, &lt;months&gt;)</t>
+  </si>
+  <si>
+    <t>返回指定月份数之前或之后的月份的最后一天的日期，该日期采用 datetime 格式。 EOMONTH 可用于计算处于月份最后一天的到期日期。</t>
+  </si>
+  <si>
+    <t>HOUR(&lt;datetime&gt;)</t>
+  </si>
+  <si>
+    <t>将小时返回为从 0 (12:00 A.M.) 到 23 (11:00 P.M.) 的数字。</t>
+  </si>
+  <si>
+    <t>MINUTE(&lt;datetime&gt;)</t>
+  </si>
+  <si>
+    <t>将分钟作为 0 到 59 之间的数字返回，给出日期和时间值。</t>
+  </si>
+  <si>
+    <t>MONTH(&lt;datetime&gt;)</t>
+  </si>
+  <si>
+    <t>将月份返回为从 1（1 月）到 12（12 月）的数字。</t>
+  </si>
+  <si>
+    <t>NOW()</t>
+  </si>
+  <si>
+    <t>在您需要在工作表上显示当前日期和时间，或者基于当前日期和时间计算某一值，并且每次打开工作表该值都更新时，NOW 函数会很有用。</t>
+  </si>
+  <si>
+    <t>SECOND(&lt;time&gt;)</t>
+  </si>
+  <si>
+    <t>将时间值中的秒数以 0 到 59 之间的数字的形式返回。</t>
+  </si>
+  <si>
+    <t>TIME(hour, minute, second)</t>
+  </si>
+  <si>
+    <t>将作为数字提供的小时、分钟和秒钟转换为 datetime 格式的时间。</t>
+  </si>
+  <si>
+    <t>TIMEVALUE(time_text)</t>
+  </si>
+  <si>
+    <t>将文本格式的时间转换为日期时间格式的时间。</t>
+  </si>
+  <si>
+    <t>WEEKDAY(&lt;date&gt;, &lt;return_type&gt;)</t>
+  </si>
+  <si>
+    <t>返回用来标识某一日期是星期几的 1 到 7 之间的数字。 默认情况下，这个星期几的范围是从 1（星期日）到 7（星期六）。</t>
+  </si>
+  <si>
+    <t>TODAY()</t>
+  </si>
+  <si>
+    <t>返回当前日期。</t>
+  </si>
+  <si>
+    <t>WEEKNUM(&lt;date&gt;, &lt;return_type&gt;)</t>
+  </si>
+  <si>
+    <t>根据 return_type 值返回给定日期和年份的周数。 周数指示该周在数字上属于一年中的何处。</t>
+  </si>
+  <si>
+    <t>YEAR(&lt;date&gt;)</t>
+  </si>
+  <si>
+    <t>以 1900-9999 范围的四位整数形式返回日期的年份。</t>
+  </si>
+  <si>
+    <t>YEARFRAC(&lt;start_date&gt;, &lt;end_date&gt;, &lt;basis&gt;)</t>
+  </si>
+  <si>
+    <t>计算两个日期之间的完整天数占全年天数的比例。 使用 YEARFRAC 工作表函数可计算要从整年的收益或负债中分配给特定期限的比例。</t>
+  </si>
+  <si>
+    <t>CONTAINS(&lt;table&gt;, &lt;columnName&gt;, &lt;value&gt;[, &lt;columnName&gt;, &lt;value&gt;]…)</t>
+  </si>
+  <si>
+    <t>如果所有引用列的结果都存在或包含在这些列中，则返回 true；否则，此函数返回 false。</t>
+  </si>
+  <si>
+    <t>ISBLANK(&lt;value&gt;)</t>
+  </si>
+  <si>
+    <t>检查某个值是否为空白，并且返回 TRUE 或 FALSE。</t>
+  </si>
+  <si>
+    <t>ISERROR(&lt;value&gt;)</t>
+  </si>
+  <si>
+    <t>检查某个值是否为错误，并且返回 TRUE 或 FALSE。</t>
+  </si>
+  <si>
+    <t>ISLOGICAL(&lt;value&gt;)</t>
+  </si>
+  <si>
+    <t>检查某个值是否是逻辑值（TRUE 或 FALSE），并且返回 TRUE 或 FALSE。</t>
+  </si>
+  <si>
+    <t>ISNONTEXT(&lt;value&gt;)</t>
+  </si>
+  <si>
+    <t>检查某个值是否不是文本（空白单元不是文本），返回 TRUE 或 FALSE。</t>
+  </si>
+  <si>
+    <t>ISNUMBER(&lt;value&gt;)</t>
+  </si>
+  <si>
+    <t>检查某个值是否为数字，并且返回 TRUE 或 FALSE。</t>
+  </si>
+  <si>
+    <t>ISTEXT(&lt;value&gt;)</t>
+  </si>
+  <si>
+    <t>检查某个值是否为文本，并且返回 TRUE 或 FALSE。</t>
+  </si>
+  <si>
+    <t>AVERAGE(&lt;column&gt;)</t>
+  </si>
+  <si>
+    <t>返回列中所有数字的平均值（算术平均值）。</t>
+  </si>
+  <si>
+    <t>AVERAGEA(&lt;column&gt;)</t>
+  </si>
+  <si>
+    <t>返回列中值的平均值（算术平均值）。 处理文本和非数字值。</t>
+  </si>
+  <si>
+    <t>AVERAGEX(&lt;table&gt;,&lt;expression&gt;)</t>
+  </si>
+  <si>
+    <t>计算对表进行求值的一组表达式的平均值（算术平均值）。</t>
+  </si>
+  <si>
+    <t>COUNT 函数计算列中包含数字的单元的数目。</t>
+  </si>
+  <si>
+    <t>COUNT(&lt;column&gt;)</t>
+  </si>
+  <si>
+    <t>COUNTA(&lt;column&gt;)</t>
+  </si>
+  <si>
+    <t>COUNTA 函数计算列中不为空的单元的数目。 它不仅对包含数值的行进行计数，还对包含非空白值（包括文本、日期和逻辑值）的行进行计数。</t>
+  </si>
+  <si>
+    <t>COUNTAX(&lt;table&gt;,&lt;expression&gt;)</t>
+  </si>
+  <si>
+    <t>COUNTAX 函数用于在对表计算表达式的结果时统计非空结果数。 即，它的作用与 COUNTA 函数类似，但它用于对表中所有行进行循环访问，并统计指定表达式计算为非空结果的行数。</t>
+  </si>
+  <si>
+    <t>COUNTBLANK(&lt;column&gt;)</t>
+  </si>
+  <si>
+    <t>计算列中空白单元的数目。</t>
+  </si>
+  <si>
+    <t>COUNTROWS(&lt;table&gt;)</t>
+  </si>
+  <si>
+    <t>COUNTROWS 函数计算指定表中的行数，或者计算表达式定义的表中的行数。</t>
+  </si>
+  <si>
+    <t>COUNTX(&lt;table&gt;,&lt;expression&gt;)</t>
+  </si>
+  <si>
+    <t>在对表计算表达式的结果时，计算包含数字或者计算结果为数字的表达式的行的数目。</t>
+  </si>
+  <si>
+    <t>DISTINCTCOUNT(&lt;column&gt;)</t>
+  </si>
+  <si>
+    <t>DISTINCTCOUNT 函数计算一个数字列中不同单元的数目。</t>
+  </si>
+  <si>
+    <t>MAX(&lt;column&gt;)</t>
+  </si>
+  <si>
+    <t>返回列中的最大数值。</t>
+  </si>
+  <si>
+    <t>MAXA(&lt;column&gt;)</t>
+  </si>
+  <si>
+    <t>返回列中的最大值。 逻辑值和空白被计算在内。</t>
+  </si>
+  <si>
+    <t>MAXX(&lt;table&gt;,&lt;expression&gt;)</t>
+  </si>
+  <si>
+    <t>为表的每一行计算表达式，并且返回最大的数值。</t>
+  </si>
+  <si>
+    <t>MINA(&lt;column&gt;)</t>
+  </si>
+  <si>
+    <t>返回列中的最小值，包括任何逻辑值和以文本形式表示的数字。</t>
+  </si>
+  <si>
+    <t>MIN(&lt;column&gt;)</t>
+  </si>
+  <si>
+    <t>返回列中的最小数值。 忽略逻辑值和文本。</t>
+  </si>
+  <si>
+    <t>MINX(&lt;table&gt;, &lt; expression&gt;)</t>
+  </si>
+  <si>
+    <t>返回通过为表的每一行计算表达式而得出的最小数值。</t>
+  </si>
+  <si>
+    <t>RANK.EQ(&lt;value&gt;, &lt;columnName&gt;[, &lt;order&gt;])</t>
+  </si>
+  <si>
+    <t>返回某个数字在数字列表中的排名。</t>
+  </si>
+  <si>
+    <t>RANKX(&lt;table&gt;, &lt;expression&gt;[, &lt;value&gt;[, &lt;order&gt;[, &lt;ties&gt;]]])</t>
+  </si>
+  <si>
+    <t>对于 table 参数中的每一行，返回某个数字在数字列表中的排名。</t>
+  </si>
+  <si>
+    <t>ROW(&lt;name&gt;, &lt;expression&gt;][,&lt;name&gt;, &lt;expression&gt;]…])</t>
+  </si>
+  <si>
+    <t>返回一个包含单一行的表，该行包括从给予每列的表达式得到的值。</t>
+  </si>
+  <si>
+    <t>SAMPLE(&lt;n_value&gt;, &lt;table&gt;, &lt;orderBy_expression&gt;, [&lt;order&gt;[, &lt;orderBy_expression&gt;, [&lt;order&gt;]]…])</t>
+  </si>
+  <si>
+    <t>从指定的表中返回一个包含 N 行的示例。</t>
+  </si>
+  <si>
+    <t>STDEV.P(&lt;ColumnName&gt;)</t>
+  </si>
+  <si>
+    <t>返回整个总体的标准偏差。</t>
+  </si>
+  <si>
+    <t>STDEV.S(&lt;ColumnName&gt;)</t>
+  </si>
+  <si>
+    <t>返回样本总体的标准偏差。</t>
+  </si>
+  <si>
+    <t>TDEVX.P(&lt;table&gt;, &lt;expression&gt;)</t>
+  </si>
+  <si>
+    <t>STDEVX.S(&lt;table&gt;, &lt;expression&gt;)</t>
+  </si>
+  <si>
+    <t>针对一系列组所请求的总计返回摘要表。</t>
+  </si>
+  <si>
+    <t>TOPN(&lt;n_value&gt;, &lt;table&gt;, &lt;orderBy_expression&gt;, [&lt;order&gt;[, &lt;orderBy_expression&gt;, [&lt;order&gt;]]…])</t>
+  </si>
+  <si>
+    <t>返回指定表的前 N 行。</t>
+  </si>
+  <si>
+    <t>VAR.P(&lt;columnName&gt;)</t>
+  </si>
+  <si>
+    <t>返回整个总体的方差。</t>
+  </si>
+  <si>
+    <t>VAR.S(&lt;columnName&gt;)</t>
+  </si>
+  <si>
+    <t>返回样本总体的方差。</t>
+  </si>
+  <si>
+    <t>VARX.P(&lt;table&gt;, &lt;expression&gt;)</t>
+  </si>
+  <si>
+    <t>VARX.S(&lt;table&gt;, &lt;expression&gt;)</t>
+  </si>
+  <si>
+    <t>CLOSINGBALANCEMONTH(&lt;expression&gt;,&lt;dates&gt;[,&lt;filter&gt;])</t>
+  </si>
+  <si>
+    <t>计算当前上下文中该月最后一个日期的 expression。</t>
+  </si>
+  <si>
+    <t>CLOSINGBALANCEQUARTER(&lt;expression&gt;,&lt;dates&gt;[,&lt;filter&gt;])</t>
+  </si>
+  <si>
+    <t>计算当前上下文中该季度最后日期的 expression。</t>
+  </si>
+  <si>
+    <t>CLOSINGBALANCEYEAR(&lt;expression&gt;,&lt;dates&gt;[,&lt;filter&gt;][,&lt;year_end_date&gt;])</t>
+  </si>
+  <si>
+    <t>计算当前上下文中该年度最后日期的 expression。</t>
+  </si>
+  <si>
+    <t>DATEADD(&lt;dates&gt;,&lt;number_of_intervals&gt;,&lt;interval&gt;)</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含由日期构成的一列，这些日期是在时间上从当前上下文中的日期前移或后移指定间隔数目的日期。</t>
+  </si>
+  <si>
+    <t>DATESBETWEEN(&lt;dates&gt;,&lt;start_date&gt;,&lt;end_date&gt;)</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含由日期构成的一列，这些日期从 start_date 开始，并且继续到 end_date。</t>
+  </si>
+  <si>
+    <t>DATESINPERIOD(&lt;dates&gt;,&lt;start_date&gt;,&lt;number_of_intervals&gt;,&lt;interval&gt;)</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含由日期构成的一列，这些日期从 start_date 开始，并且继续到指定的 number_of_intervals。</t>
+  </si>
+  <si>
+    <t>DATESMTD(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含当前上下文中本月截止到现在的日期列。</t>
+  </si>
+  <si>
+    <t>DATESQTD(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含当前上下文中本季度截止到现在的日期列。</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含当前上下文中本年度截止到现在的日期列。</t>
+  </si>
+  <si>
+    <t>DATESYTD(&lt;dates&gt; [,&lt;year_end_date&gt;])</t>
+  </si>
+  <si>
+    <t>ENDOFMONTH(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回当前上下文中指定日期列的相对应月份的最后日期。</t>
+  </si>
+  <si>
+    <t>ENDOFQUARTER(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回当前上下文中指定日期列的相对应季度的最后日期。</t>
+  </si>
+  <si>
+    <t>ENDOFYEAR(&lt;dates&gt; [,&lt;year_end_date&gt;])</t>
+  </si>
+  <si>
+    <t>返回当前上下文中指定日期列的相对应年份的最后日期。</t>
+  </si>
+  <si>
+    <t>FIRSTDATE(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回当前上下文中指定日期列的第一个日期。</t>
+  </si>
+  <si>
+    <t>FIRSTNONBLANK(&lt;column&gt;,&lt;expression&gt;)</t>
+  </si>
+  <si>
+    <t>返回按当前上下文筛选的列 column（其中表达式不为空白）中的第一个值。</t>
+  </si>
+  <si>
+    <t>LASTDATE(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回当前上下文中指定日期列的最后日期。</t>
+  </si>
+  <si>
+    <t>LASTNONBLANK(&lt;column&gt;,&lt;expression&gt;)</t>
+  </si>
+  <si>
+    <t>返回按当前上下文筛选的列 column（其中表达式不为空白）中的最后一个值。</t>
+  </si>
+  <si>
+    <t>NEXTDAY(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含的一列具有当前上下文中基于 dates 列中指定的第一个日期的下一天中的所有日期。</t>
+  </si>
+  <si>
+    <t>NEXTMONTH(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含的一列具有当前上下文中基于 dates 列中第一个日期的下一月中的所有日期。</t>
+  </si>
+  <si>
+    <t>NEXTQUARTER(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含的一列具有当前上下文中基于 dates 列中指定的第一个日期的下一季度中的所有日期。</t>
+  </si>
+  <si>
+    <t>NEXTYEAR(&lt;dates&gt;[,&lt;year_end_date&gt;])</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含的一列具有当前上下文中基于 dates 列中第一个日期的下一年中的所有日期。</t>
+  </si>
+  <si>
+    <t>OPENINGBALANCEMONTH(&lt;expression&gt;,&lt;dates&gt;[,&lt;filter&gt;])</t>
+  </si>
+  <si>
+    <t>计算当前上下文中该月第一个日期的 expression。</t>
+  </si>
+  <si>
+    <t>OPENINGBALANCEQUARTER(&lt;expression&gt;,&lt;dates&gt;[,&lt;filter&gt;])</t>
+  </si>
+  <si>
+    <t>计算当前上下文中该季度第一个日期的 expression。</t>
+  </si>
+  <si>
+    <t>OPENINGBALANCEYEAR(&lt;expression&gt;,&lt;dates&gt;[,&lt;filter&gt;][,&lt;year_end_date&gt;])</t>
+  </si>
+  <si>
+    <t>计算当前上下文中该年度第一个日期的 expression。</t>
+  </si>
+  <si>
+    <t>PARALLELPERIOD(&lt;dates&gt;,&lt;number_of_intervals&gt;,&lt;interval&gt;)</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含由日期构成的一列，这些日期表示与当前上下文中指定的 dates 列中的日期并行的期间，该列中具有在时间中前移或后移某个数目的间隔的日期。</t>
+  </si>
+  <si>
+    <t>PREVIOUSDAY(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含的一列具有表示当前上下文的 dates 列中第一个日期之前那一天的所有日期。</t>
+  </si>
+  <si>
+    <t>PREVIOUSMONTH(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含的一列具有当前上下文中基于 dates 列中第一个日期的上个月中的所有日期。</t>
+  </si>
+  <si>
+    <t>PREVIOUSQUARTER(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含的一列具有当前上下文中基于 dates 列中第一个日期的上一季度中的所有日期。</t>
+  </si>
+  <si>
+    <t>PREVIOUSYEAR(&lt;dates&gt;[,&lt;year_end_date&gt;])</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含的一列具有当前上下文中来自上一年的所有日期，在 dates 列中给出最后日期。</t>
+  </si>
+  <si>
+    <t>SAMEPERIODLASTYEAR(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回一个表，该表包含由日期构成的一列，这些日期是在时间上从当前上下文中指定的 dates 列中的日期移回一年的日期。</t>
+  </si>
+  <si>
+    <t>STARTOFMONTH(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回当前上下文中指定日期列的相对应月份的第一个日期。</t>
+  </si>
+  <si>
+    <t>STARTOFQUARTER(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回当前上下文中指定日期列的相对应季度的第一个日期。</t>
+  </si>
+  <si>
+    <t>STARTOFYEAR(&lt;dates&gt;)</t>
+  </si>
+  <si>
+    <t>返回当前上下文中指定日期列的相对应年份的第一个日期。</t>
+  </si>
+  <si>
+    <t>TOTALMTD(&lt;expression&gt;,&lt;dates&gt;[,&lt;filter&gt;])</t>
+  </si>
+  <si>
+    <t>计算当前上下文中当月至今的 expression 的值。</t>
+  </si>
+  <si>
+    <t>TOTALQTD(&lt;expression&gt;,&lt;dates&gt;[,&lt;filter&gt;])</t>
+  </si>
+  <si>
+    <t>计算当前上下文中当季度至今中日期的 expression 的值。</t>
+  </si>
+  <si>
+    <t>TOTALYTD(&lt;expression&gt;,&lt;dates&gt;[,&lt;filter&gt;][,&lt;year_end_date&gt;])</t>
+  </si>
+  <si>
+    <t>计算当前上下文中 expression 的年初至今值。</t>
+  </si>
+  <si>
+    <t>SUMMARIZE(&lt;table&gt;, &lt;groupBy_columnName&gt;[, &lt;groupBy_columnName&gt;]…[, &lt;name&gt;, &lt;expression&gt;]…)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
@@ -34,7 +742,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,23 +750,59 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -343,28 +1087,1023 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="57.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="91.125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="62.875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="80.125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="46.25" style="6" customWidth="1"/>
+    <col min="2" max="2" width="94.75" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="49.5" style="5" customWidth="1"/>
+    <col min="2" max="2" width="85.875" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="54.625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="88.125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.15"/>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="67.125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="85.625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>